--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96158</v>
+        <v>96165</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129271369</v>
+        <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567690</v>
+        <v>567685</v>
       </c>
       <c r="R12" t="n">
-        <v>6507636</v>
+        <v>6507629</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129274008</v>
+        <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567685</v>
+        <v>567690</v>
       </c>
       <c r="R13" t="n">
-        <v>6507629</v>
+        <v>6507636</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91953</v>
+        <v>91960</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R4" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B5" t="n">
-        <v>92871</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R5" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96165</v>
+        <v>96167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129271576</v>
+        <v>129274008</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567755</v>
+        <v>567685</v>
       </c>
       <c r="R11" t="n">
-        <v>6507685</v>
+        <v>6507629</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129274008</v>
+        <v>129271576</v>
       </c>
       <c r="B12" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567685</v>
+        <v>567755</v>
       </c>
       <c r="R12" t="n">
-        <v>6507629</v>
+        <v>6507685</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91960</v>
+        <v>91962</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,6 +1975,1157 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129346498</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92177</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Nedre herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>567673</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6507645</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129346493</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96274</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Nedre herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>567760</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6507760</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129348675</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92835</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>567788</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6507743</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129338383</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92873</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>567628</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6507641</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129339186</v>
+      </c>
+      <c r="B19" t="n">
+        <v>92835</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>567754</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6507664</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129338831</v>
+      </c>
+      <c r="B20" t="n">
+        <v>105741</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>567680</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6507618</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>129348519</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>567686</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6507647</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>129348644</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>567748</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6507663</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>129339083</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nedre herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>567673</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6507645</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Malin Ringqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129340660</v>
+      </c>
+      <c r="B24" t="n">
+        <v>96167</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>567623</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6507640</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129348724</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98678</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>567722</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6507702</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2084,10 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129346493</v>
+        <v>129348675</v>
       </c>
       <c r="B16" t="n">
-        <v>96274</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2095,37 +2095,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567760</v>
+        <v>567788</v>
       </c>
       <c r="R16" t="n">
-        <v>6507760</v>
+        <v>6507743</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2152,98 +2163,78 @@
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-26</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>11:21</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2281,51 +2272,50 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2335,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2397,10 +2387,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129339186</v>
+        <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>105741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,37 +2398,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567754</v>
+        <v>567680</v>
       </c>
       <c r="R19" t="n">
-        <v>6507664</v>
+        <v>6507618</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2494,37 +2493,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>105741</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2532,19 +2531,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R20" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2582,25 +2584,26 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129348519</v>
+        <v>129348644</v>
       </c>
       <c r="B21" t="n">
         <v>98678</v>
@@ -2630,7 +2633,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2647,10 +2650,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567686</v>
+        <v>567748</v>
       </c>
       <c r="R21" t="n">
-        <v>6507647</v>
+        <v>6507663</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2710,7 +2713,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129348644</v>
+        <v>129339083</v>
       </c>
       <c r="B22" t="n">
         <v>98678</v>
@@ -2740,27 +2743,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567748</v>
+        <v>567673</v>
       </c>
       <c r="R22" t="n">
-        <v>6507663</v>
+        <v>6507645</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2801,71 +2796,66 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Malin Ringqvist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Malin Ringqvist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129339083</v>
+        <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>96167</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nedre herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567673</v>
+        <v>567623</v>
       </c>
       <c r="R23" t="n">
-        <v>6507645</v>
+        <v>6507640</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2909,60 +2899,72 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129340660</v>
+        <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>96167</v>
+        <v>98678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567623</v>
+        <v>567722</v>
       </c>
       <c r="R24" t="n">
-        <v>6507640</v>
+        <v>6507702</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3000,131 +3002,22 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>129348724</v>
-      </c>
-      <c r="B25" t="n">
-        <v>98678</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Nedre Herrgölen, Ög</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>567722</v>
-      </c>
-      <c r="R25" t="n">
-        <v>6507702</v>
-      </c>
-      <c r="S25" t="n">
-        <v>10</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Norrköping</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Kvillinge</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Anette Källman</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Anette Källman</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R4" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92859</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R5" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>92859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129274008</v>
+        <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567685</v>
+        <v>567755</v>
       </c>
       <c r="R11" t="n">
-        <v>6507629</v>
+        <v>6507685</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129271576</v>
+        <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567755</v>
+        <v>567685</v>
       </c>
       <c r="R12" t="n">
-        <v>6507685</v>
+        <v>6507629</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91962</v>
+        <v>91971</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92177</v>
+        <v>92192</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2112,31 +2112,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2174,67 +2163,77 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
-        <v>92873</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2272,50 +2271,51 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339186</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567754</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2390,7 +2390,7 @@
         <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>105741</v>
+        <v>105767</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96167</v>
+        <v>96193</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91971</v>
+        <v>91972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B16" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2112,20 +2112,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2163,77 +2174,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,51 +2272,50 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2387,37 +2387,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B19" t="n">
-        <v>105767</v>
+        <v>98705</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,19 +2425,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R19" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2475,55 +2478,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B20" t="n">
-        <v>98704</v>
+        <v>105769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2531,22 +2535,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R20" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2584,19 +2585,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96193</v>
+        <v>96194</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129271576</v>
+        <v>129271369</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567755</v>
+        <v>567690</v>
       </c>
       <c r="R11" t="n">
-        <v>6507685</v>
+        <v>6507636</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129274008</v>
+        <v>129271576</v>
       </c>
       <c r="B12" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567685</v>
+        <v>567755</v>
       </c>
       <c r="R12" t="n">
-        <v>6507629</v>
+        <v>6507685</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129271369</v>
+        <v>129274008</v>
       </c>
       <c r="B13" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567690</v>
+        <v>567685</v>
       </c>
       <c r="R13" t="n">
-        <v>6507636</v>
+        <v>6507629</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2084,59 +2084,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92822</v>
+        <v>92860</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R16" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2174,51 +2163,50 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B17" t="n">
-        <v>92860</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2228,10 +2216,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R17" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2290,7 +2278,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B18" t="n">
         <v>92822</v>
@@ -2318,20 +2306,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R18" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2369,18 +2368,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
         <v>129348519</v>
       </c>
       <c r="B19" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         <v>129338831</v>
       </c>
       <c r="B20" t="n">
-        <v>105769</v>
+        <v>105770</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96194</v>
+        <v>96195</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R4" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B5" t="n">
-        <v>92860</v>
+        <v>92825</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R5" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96195</v>
+        <v>96199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1562,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129271369</v>
+        <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567690</v>
+        <v>567755</v>
       </c>
       <c r="R11" t="n">
-        <v>6507636</v>
+        <v>6507685</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129271576</v>
+        <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567755</v>
+        <v>567685</v>
       </c>
       <c r="R12" t="n">
-        <v>6507685</v>
+        <v>6507629</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129274008</v>
+        <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567685</v>
+        <v>567690</v>
       </c>
       <c r="R13" t="n">
-        <v>6507629</v>
+        <v>6507636</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91972</v>
+        <v>91975</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92193</v>
+        <v>92196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>129339186</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,37 +2387,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>98706</v>
+        <v>105774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,22 +2425,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R19" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2478,56 +2475,55 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>105770</v>
+        <v>98710</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2535,19 +2531,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R20" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2585,18 +2584,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,48 +2814,60 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129340660</v>
+        <v>129348724</v>
       </c>
       <c r="B23" t="n">
-        <v>96195</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567623</v>
+        <v>567722</v>
       </c>
       <c r="R23" t="n">
-        <v>6507640</v>
+        <v>6507702</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2893,78 +2905,67 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129348724</v>
+        <v>129340660</v>
       </c>
       <c r="B24" t="n">
-        <v>98706</v>
+        <v>96199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567722</v>
+        <v>567623</v>
       </c>
       <c r="R24" t="n">
-        <v>6507702</v>
+        <v>6507640</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3002,19 +3003,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R4" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92825</v>
+        <v>92865</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R5" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92863</v>
+        <v>92865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91975</v>
+        <v>91977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92196</v>
+        <v>92198</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>92827</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,20 +2209,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2260,77 +2271,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>92865</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2368,56 +2369,55 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B19" t="n">
-        <v>105774</v>
+        <v>98712</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,19 +2425,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R19" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2475,55 +2478,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B20" t="n">
-        <v>98710</v>
+        <v>105776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2531,22 +2535,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R20" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2584,19 +2585,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129348724</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>129340660</v>
       </c>
       <c r="B24" t="n">
-        <v>96199</v>
+        <v>96201</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R4" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B5" t="n">
-        <v>92865</v>
+        <v>92831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R5" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96201</v>
+        <v>96205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92865</v>
+        <v>92869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91977</v>
+        <v>91981</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92198</v>
+        <v>92202</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92827</v>
+        <v>92869</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567628</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B17" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,31 +2209,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,67 +2260,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92865</v>
+        <v>92831</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2369,55 +2368,56 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>98712</v>
+        <v>105780</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,22 +2425,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R19" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2478,56 +2475,55 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>105776</v>
+        <v>98716</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2535,19 +2531,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R20" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2585,18 +2584,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,60 +2814,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129348724</v>
+        <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>96205</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567722</v>
+        <v>567623</v>
       </c>
       <c r="R23" t="n">
-        <v>6507702</v>
+        <v>6507640</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2905,67 +2893,78 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129340660</v>
+        <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>96201</v>
+        <v>98716</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567623</v>
+        <v>567722</v>
       </c>
       <c r="R24" t="n">
-        <v>6507640</v>
+        <v>6507702</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3003,18 +3002,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R4" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92831</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R5" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>129339186</v>
       </c>
       <c r="B17" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,7 +2390,7 @@
         <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>105780</v>
+        <v>105790</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96205</v>
+        <v>96213</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R4" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R5" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92870</v>
+        <v>92832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
         <v>92832</v>
@@ -2209,20 +2209,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2260,77 +2271,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>92870</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2368,19 +2369,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R4" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92832</v>
+        <v>92870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R5" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92832</v>
+        <v>92870</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567628</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B17" t="n">
         <v>92832</v>
@@ -2209,31 +2209,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,67 +2260,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92870</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2369,18 +2368,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2814,48 +2814,60 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129340660</v>
+        <v>129348724</v>
       </c>
       <c r="B23" t="n">
-        <v>96213</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567623</v>
+        <v>567722</v>
       </c>
       <c r="R23" t="n">
-        <v>6507640</v>
+        <v>6507702</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2893,78 +2905,67 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129348724</v>
+        <v>129340660</v>
       </c>
       <c r="B24" t="n">
-        <v>98724</v>
+        <v>96213</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567722</v>
+        <v>567623</v>
       </c>
       <c r="R24" t="n">
-        <v>6507702</v>
+        <v>6507640</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3002,19 +3003,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96213</v>
+        <v>96216</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92870</v>
+        <v>92873</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91982</v>
+        <v>91985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92870</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,20 +2209,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2260,77 +2271,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2368,19 +2369,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2390,7 +2390,7 @@
         <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>105790</v>
+        <v>105793</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2814,60 +2814,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129348724</v>
+        <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>96216</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567722</v>
+        <v>567623</v>
       </c>
       <c r="R23" t="n">
-        <v>6507702</v>
+        <v>6507640</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2905,67 +2893,78 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129340660</v>
+        <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>96213</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567623</v>
+        <v>567722</v>
       </c>
       <c r="R24" t="n">
-        <v>6507640</v>
+        <v>6507702</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3003,18 +3002,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567628</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B17" t="n">
         <v>92835</v>
@@ -2209,31 +2209,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,67 +2260,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2369,18 +2368,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R4" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R5" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
         <v>92835</v>
@@ -2209,20 +2209,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2260,77 +2271,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2368,19 +2369,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2814,48 +2814,60 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129340660</v>
+        <v>129348724</v>
       </c>
       <c r="B23" t="n">
-        <v>96216</v>
+        <v>98727</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567623</v>
+        <v>567722</v>
       </c>
       <c r="R23" t="n">
-        <v>6507640</v>
+        <v>6507702</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2893,78 +2905,67 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129348724</v>
+        <v>129340660</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>96216</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567722</v>
+        <v>567623</v>
       </c>
       <c r="R24" t="n">
-        <v>6507702</v>
+        <v>6507640</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3002,19 +3003,18 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R4" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R5" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2387,37 +2387,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B19" t="n">
-        <v>105793</v>
+        <v>98727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,19 +2425,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R19" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2475,55 +2478,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B20" t="n">
-        <v>98727</v>
+        <v>105793</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2531,22 +2535,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R20" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2584,19 +2585,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2814,60 +2814,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129348724</v>
+        <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>98727</v>
+        <v>96216</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567722</v>
+        <v>567623</v>
       </c>
       <c r="R23" t="n">
-        <v>6507702</v>
+        <v>6507640</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2905,67 +2893,78 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129340660</v>
+        <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>96216</v>
+        <v>98727</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567623</v>
+        <v>567722</v>
       </c>
       <c r="R24" t="n">
-        <v>6507640</v>
+        <v>6507702</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3003,18 +3002,19 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R4" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B5" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R5" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -2181,59 +2181,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>92873</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,67 +2260,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92873</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2369,18 +2368,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -2084,7 +2084,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B16" t="n">
         <v>92835</v>
@@ -2112,20 +2112,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2163,18 +2174,19 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2278,7 +2290,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B18" t="n">
         <v>92835</v>
@@ -2306,31 +2318,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R18" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2368,19 +2369,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,32 +883,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129273293</v>
+        <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92873</v>
+        <v>92863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,13 +918,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567760</v>
+        <v>567692</v>
       </c>
       <c r="R4" t="n">
-        <v>6507662</v>
+        <v>6507635</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,32 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129271284</v>
+        <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92835</v>
+        <v>92901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567692</v>
+        <v>567760</v>
       </c>
       <c r="R5" t="n">
-        <v>6507635</v>
+        <v>6507662</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91574</v>
+        <v>91602</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92873</v>
+        <v>92901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>91985</v>
+        <v>92013</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92206</v>
+        <v>92234</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,10 +2084,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92835</v>
+        <v>92863</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2112,31 +2112,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2174,67 +2163,77 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
-        <v>92873</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2272,50 +2271,51 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129339186</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2325,10 +2325,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567754</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2387,37 +2387,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>98727</v>
+        <v>105822</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,22 +2425,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R19" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2478,56 +2475,55 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>105793</v>
+        <v>98756</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2535,19 +2531,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R20" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2585,18 +2584,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96216</v>
+        <v>96245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92901</v>
+        <v>92907</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>92013</v>
+        <v>92019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92234</v>
+        <v>92240</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92863</v>
+        <v>92907</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567628</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>92869</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,31 +2209,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,67 +2260,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92901</v>
+        <v>92869</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2369,55 +2368,56 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B19" t="n">
-        <v>105822</v>
+        <v>98768</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,19 +2425,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R19" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2475,55 +2478,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B20" t="n">
-        <v>98756</v>
+        <v>105834</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2531,22 +2535,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R20" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2584,19 +2585,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96245</v>
+        <v>96257</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,6 +3018,1037 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129715546</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91601</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>567701</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6507721</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129715556</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96210</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>210</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6507735</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>129715425</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92019</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>567751</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6507643</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>129715489</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>567736</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6507677</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>129715522</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91608</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>567730</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6507699</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>129715500</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>567741</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6507694</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>129716072</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92861</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>567681</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6507630</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>129715241</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>567688</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6507631</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>129715396</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>567695</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6507637</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>129715409</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91608</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>567740</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6507631</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>129271263</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129271284</v>
       </c>
       <c r="B4" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129273293</v>
       </c>
       <c r="B5" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>129271131</v>
       </c>
       <c r="B6" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>129273672</v>
       </c>
       <c r="B7" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,7 +1274,7 @@
         <v>129271951</v>
       </c>
       <c r="B8" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
         <v>129273994</v>
       </c>
       <c r="B9" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         <v>129274017</v>
       </c>
       <c r="B10" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1565,7 +1565,7 @@
         <v>129271576</v>
       </c>
       <c r="B11" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
         <v>129274008</v>
       </c>
       <c r="B12" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>129271369</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>129273599</v>
       </c>
       <c r="B14" t="n">
-        <v>92019</v>
+        <v>92020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92907</v>
+        <v>92908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
         <v>129339186</v>
       </c>
       <c r="B17" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92869</v>
+        <v>92870</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,37 +2387,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B19" t="n">
-        <v>98768</v>
+        <v>105835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,22 +2425,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R19" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2478,56 +2475,55 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B20" t="n">
-        <v>105834</v>
+        <v>98769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2535,19 +2531,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R20" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2585,18 +2584,19 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96257</v>
+        <v>96258</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91601</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96210</v>
+        <v>96211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>92019</v>
+        <v>92020</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92861</v>
+        <v>92862</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -1980,7 +1980,7 @@
         <v>129346498</v>
       </c>
       <c r="B15" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92908</v>
+        <v>92875</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2209,20 +2209,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2260,77 +2271,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92870</v>
+        <v>92913</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2368,56 +2369,55 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129338831</v>
+        <v>129348519</v>
       </c>
       <c r="B19" t="n">
-        <v>105835</v>
+        <v>98774</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>69</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2425,19 +2425,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567680</v>
+        <v>567686</v>
       </c>
       <c r="R19" t="n">
-        <v>6507618</v>
+        <v>6507647</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2475,55 +2478,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129348519</v>
+        <v>129338831</v>
       </c>
       <c r="B20" t="n">
-        <v>98769</v>
+        <v>105840</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2531,22 +2535,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567686</v>
+        <v>567680</v>
       </c>
       <c r="R20" t="n">
-        <v>6507647</v>
+        <v>6507618</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2584,19 +2585,18 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2606,7 +2606,7 @@
         <v>129348644</v>
       </c>
       <c r="B21" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>129339083</v>
       </c>
       <c r="B22" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129340660</v>
       </c>
       <c r="B23" t="n">
-        <v>96258</v>
+        <v>96263</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129348724</v>
       </c>
       <c r="B24" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>91607</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96211</v>
+        <v>96216</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>92020</v>
+        <v>92025</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92862</v>
+        <v>92867</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129338383</v>
       </c>
       <c r="B16" t="n">
-        <v>92875</v>
+        <v>92913</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567628</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129339186</v>
       </c>
       <c r="B17" t="n">
         <v>92875</v>
@@ -2209,31 +2209,20 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567754</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507664</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2271,67 +2260,77 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129348675</v>
       </c>
       <c r="B18" t="n">
-        <v>92913</v>
+        <v>92875</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567788</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507743</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2369,18 +2368,19 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -2084,32 +2084,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129338383</v>
+        <v>129339186</v>
       </c>
       <c r="B16" t="n">
-        <v>92913</v>
+        <v>92875</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567628</v>
+        <v>567754</v>
       </c>
       <c r="R16" t="n">
-        <v>6507641</v>
+        <v>6507664</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2181,7 +2181,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129339186</v>
+        <v>129348675</v>
       </c>
       <c r="B17" t="n">
         <v>92875</v>
@@ -2209,20 +2209,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567754</v>
+        <v>567788</v>
       </c>
       <c r="R17" t="n">
-        <v>6507664</v>
+        <v>6507743</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2260,77 +2271,67 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129348675</v>
+        <v>129338383</v>
       </c>
       <c r="B18" t="n">
-        <v>92875</v>
+        <v>92913</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567788</v>
+        <v>567628</v>
       </c>
       <c r="R18" t="n">
-        <v>6507743</v>
+        <v>6507641</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2368,19 +2369,18 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3228,37 +3228,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129715425</v>
+        <v>129715489</v>
       </c>
       <c r="B27" t="n">
-        <v>92025</v>
+        <v>98774</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567751</v>
+        <v>567736</v>
       </c>
       <c r="R27" t="n">
-        <v>6507643</v>
+        <v>6507677</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3329,42 +3334,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129715489</v>
+        <v>129715425</v>
       </c>
       <c r="B28" t="n">
-        <v>98774</v>
+        <v>92025</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567736</v>
+        <v>567751</v>
       </c>
       <c r="R28" t="n">
-        <v>6507677</v>
+        <v>6507643</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91607</v>
+        <v>91611</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96216</v>
+        <v>96220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,42 +3228,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129715489</v>
+        <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>98774</v>
+        <v>92029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567736</v>
+        <v>567751</v>
       </c>
       <c r="R27" t="n">
-        <v>6507677</v>
+        <v>6507643</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3334,37 +3329,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129715425</v>
+        <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>92025</v>
+        <v>98778</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567751</v>
+        <v>567736</v>
       </c>
       <c r="R28" t="n">
-        <v>6507643</v>
+        <v>6507677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92867</v>
+        <v>92871</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96220</v>
+        <v>96222</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>92029</v>
+        <v>92031</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4050,6 +4050,241 @@
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>129866820</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>567689</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6507637</v>
+      </c>
+      <c r="S35" t="n">
+        <v>19</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>E-Nor-0874</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Sammanställt av 6 rapporter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Lena Lundin Johansson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>129866819</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98780</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>567745</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6507685</v>
+      </c>
+      <c r="S36" t="n">
+        <v>32</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>E-Nor-0875</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Sammanställt av 5 rapporter</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Karin Nyström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3228,37 +3228,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129715425</v>
+        <v>129715489</v>
       </c>
       <c r="B27" t="n">
-        <v>92031</v>
+        <v>98780</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567751</v>
+        <v>567736</v>
       </c>
       <c r="R27" t="n">
-        <v>6507643</v>
+        <v>6507677</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3329,42 +3334,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129715489</v>
+        <v>129715425</v>
       </c>
       <c r="B28" t="n">
-        <v>98780</v>
+        <v>92031</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567736</v>
+        <v>567751</v>
       </c>
       <c r="R28" t="n">
-        <v>6507677</v>
+        <v>6507643</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96222</v>
+        <v>96232</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129715489</v>
       </c>
       <c r="B27" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129866820</v>
       </c>
       <c r="B35" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>129866819</v>
       </c>
       <c r="B36" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3228,42 +3228,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129715489</v>
+        <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>98790</v>
+        <v>92031</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567736</v>
+        <v>567751</v>
       </c>
       <c r="R27" t="n">
-        <v>6507677</v>
+        <v>6507643</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3334,37 +3329,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129715425</v>
+        <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>92031</v>
+        <v>98790</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567751</v>
+        <v>567736</v>
       </c>
       <c r="R28" t="n">
-        <v>6507643</v>
+        <v>6507677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -4055,7 +4055,7 @@
         <v>129866820</v>
       </c>
       <c r="B35" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4170,7 +4170,7 @@
         <v>129866819</v>
       </c>
       <c r="B36" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91613</v>
+        <v>91616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96232</v>
+        <v>96236</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>92031</v>
+        <v>92034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92873</v>
+        <v>92876</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91620</v>
+        <v>91623</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -4052,7 +4052,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129866820</v>
+        <v>129866819</v>
       </c>
       <c r="B35" t="n">
         <v>98794</v>
@@ -4082,7 +4082,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4091,13 +4096,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567689</v>
+        <v>567745</v>
       </c>
       <c r="R35" t="n">
-        <v>6507637</v>
+        <v>6507685</v>
       </c>
       <c r="S35" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4121,22 +4126,22 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>E-Nor-0874</t>
+          <t>E-Nor-0875</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Sammanställt av 6 rapporter</t>
+          <t>Sammanställt av 5 rapporter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4156,7 +4161,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4167,7 +4172,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129866819</v>
+        <v>129866820</v>
       </c>
       <c r="B36" t="n">
         <v>98794</v>
@@ -4197,12 +4202,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4211,13 +4211,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567745</v>
+        <v>567689</v>
       </c>
       <c r="R36" t="n">
-        <v>6507685</v>
+        <v>6507637</v>
       </c>
       <c r="S36" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4241,22 +4241,22 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>E-Nor-0875</t>
+          <t>E-Nor-0874</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Sammanställt av 5 rapporter</t>
+          <t>Sammanställt av 6 rapporter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91616</v>
+        <v>91619</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96236</v>
+        <v>96239</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,37 +3228,42 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129715425</v>
+        <v>129715489</v>
       </c>
       <c r="B27" t="n">
-        <v>92034</v>
+        <v>98797</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3266,10 +3271,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567751</v>
+        <v>567736</v>
       </c>
       <c r="R27" t="n">
-        <v>6507643</v>
+        <v>6507677</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3329,42 +3334,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129715489</v>
+        <v>129715425</v>
       </c>
       <c r="B28" t="n">
-        <v>98794</v>
+        <v>92037</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567736</v>
+        <v>567751</v>
       </c>
       <c r="R28" t="n">
-        <v>6507677</v>
+        <v>6507643</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92876</v>
+        <v>92879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129866819</v>
       </c>
       <c r="B35" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129866820</v>
       </c>
       <c r="B36" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91619</v>
+        <v>91620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96239</v>
+        <v>96240</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3228,42 +3228,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129715489</v>
+        <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>98797</v>
+        <v>92038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3271,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567736</v>
+        <v>567751</v>
       </c>
       <c r="R27" t="n">
-        <v>6507677</v>
+        <v>6507643</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3334,37 +3329,42 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129715425</v>
+        <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>92037</v>
+        <v>98798</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567751</v>
+        <v>567736</v>
       </c>
       <c r="R28" t="n">
-        <v>6507643</v>
+        <v>6507677</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92879</v>
+        <v>92880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91626</v>
+        <v>91627</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129866819</v>
       </c>
       <c r="B35" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129866820</v>
       </c>
       <c r="B36" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -3024,7 +3024,7 @@
         <v>129715546</v>
       </c>
       <c r="B25" t="n">
-        <v>91620</v>
+        <v>91637</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3125,7 +3125,7 @@
         <v>129715556</v>
       </c>
       <c r="B26" t="n">
-        <v>96240</v>
+        <v>96257</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>129715425</v>
       </c>
       <c r="B27" t="n">
-        <v>92038</v>
+        <v>92055</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
         <v>129715489</v>
       </c>
       <c r="B28" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>129715522</v>
       </c>
       <c r="B29" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>129715500</v>
       </c>
       <c r="B30" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3645,7 +3645,7 @@
         <v>129716072</v>
       </c>
       <c r="B31" t="n">
-        <v>92880</v>
+        <v>92897</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
         <v>129715241</v>
       </c>
       <c r="B32" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>129715396</v>
       </c>
       <c r="B33" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>129715409</v>
       </c>
       <c r="B34" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4055,7 +4055,7 @@
         <v>129866819</v>
       </c>
       <c r="B35" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129866820</v>
       </c>
       <c r="B36" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -4055,7 +4055,7 @@
         <v>129866819</v>
       </c>
       <c r="B35" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129866820</v>
       </c>
       <c r="B36" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -4055,7 +4055,7 @@
         <v>129866819</v>
       </c>
       <c r="B35" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>129866820</v>
       </c>
       <c r="B36" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129273165</v>
+        <v>129715556</v>
       </c>
       <c r="B2" t="n">
-        <v>5177</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567782</v>
+        <v>567573</v>
       </c>
       <c r="R2" t="n">
-        <v>6507769</v>
+        <v>6507735</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,28 +762,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129271263</v>
+        <v>129715546</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,46 +792,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567692</v>
+        <v>567701</v>
       </c>
       <c r="R3" t="n">
-        <v>6507635</v>
+        <v>6507721</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +849,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,28 +863,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129271284</v>
+        <v>129273672</v>
       </c>
       <c r="B4" t="n">
-        <v>92870</v>
+        <v>96601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -918,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567692</v>
+        <v>567744</v>
       </c>
       <c r="R4" t="n">
-        <v>6507635</v>
+        <v>6507640</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,32 +979,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129273293</v>
+        <v>129340660</v>
       </c>
       <c r="B5" t="n">
-        <v>92908</v>
+        <v>96601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1015,13 +1014,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>567760</v>
+        <v>567623</v>
       </c>
       <c r="R5" t="n">
-        <v>6507662</v>
+        <v>6507640</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1045,12 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129271131</v>
+        <v>129716072</v>
       </c>
       <c r="B6" t="n">
-        <v>92908</v>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1088,37 +1087,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>567645</v>
+        <v>567681</v>
       </c>
       <c r="R6" t="n">
-        <v>6507641</v>
+        <v>6507630</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1142,12 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1156,50 +1162,51 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129273672</v>
+        <v>129271284</v>
       </c>
       <c r="B7" t="n">
-        <v>96258</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1209,10 +1216,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>567744</v>
+        <v>567692</v>
       </c>
       <c r="R7" t="n">
-        <v>6507640</v>
+        <v>6507635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,10 +1278,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129271951</v>
+        <v>129339186</v>
       </c>
       <c r="B8" t="n">
-        <v>91609</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1282,21 +1289,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1306,10 +1313,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>567801</v>
+        <v>567754</v>
       </c>
       <c r="R8" t="n">
-        <v>6507748</v>
+        <v>6507664</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -1336,12 +1343,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1368,10 +1375,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129273994</v>
+        <v>129348675</v>
       </c>
       <c r="B9" t="n">
-        <v>91609</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1379,37 +1386,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>567710</v>
+        <v>567788</v>
       </c>
       <c r="R9" t="n">
-        <v>6507621</v>
+        <v>6507743</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1433,12 +1451,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1447,50 +1465,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129274017</v>
+        <v>129273599</v>
       </c>
       <c r="B10" t="n">
-        <v>92908</v>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1500,13 +1519,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>567682</v>
+        <v>567744</v>
       </c>
       <c r="R10" t="n">
-        <v>6507630</v>
+        <v>6507640</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1562,57 +1581,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129271576</v>
+        <v>129715425</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>92348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>567755</v>
+        <v>567751</v>
       </c>
       <c r="R11" t="n">
-        <v>6507685</v>
+        <v>6507643</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1636,12 +1649,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1650,75 +1663,67 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129274008</v>
+        <v>129271951</v>
       </c>
       <c r="B12" t="n">
-        <v>98769</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>567685</v>
+        <v>567801</v>
       </c>
       <c r="R12" t="n">
-        <v>6507629</v>
+        <v>6507748</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1774,57 +1779,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129271369</v>
+        <v>129273994</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>567690</v>
+        <v>567710</v>
       </c>
       <c r="R13" t="n">
-        <v>6507636</v>
+        <v>6507621</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1880,48 +1876,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129273599</v>
+        <v>129715409</v>
       </c>
       <c r="B14" t="n">
-        <v>92020</v>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>567744</v>
+        <v>567740</v>
       </c>
       <c r="R14" t="n">
-        <v>6507640</v>
+        <v>6507631</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1945,12 +1944,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1959,66 +1958,70 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129346498</v>
+        <v>129715522</v>
       </c>
       <c r="B15" t="n">
-        <v>92246</v>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Nedre herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>567673</v>
+        <v>567730</v>
       </c>
       <c r="R15" t="n">
-        <v>6507645</v>
+        <v>6507699</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2042,22 +2045,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>11:34</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2066,50 +2059,51 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Lena Lundin Johansson, Emma Nordenberg</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129339186</v>
+        <v>129271131</v>
       </c>
       <c r="B16" t="n">
-        <v>92875</v>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2119,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>567754</v>
+        <v>567645</v>
       </c>
       <c r="R16" t="n">
-        <v>6507664</v>
+        <v>6507641</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2149,12 +2143,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2181,59 +2175,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129348675</v>
+        <v>129273293</v>
       </c>
       <c r="B17" t="n">
-        <v>92875</v>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>567788</v>
+        <v>567760</v>
       </c>
       <c r="R17" t="n">
-        <v>6507743</v>
+        <v>6507662</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2257,12 +2240,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2271,29 +2254,28 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129338383</v>
+        <v>129274017</v>
       </c>
       <c r="B18" t="n">
-        <v>92913</v>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2325,13 +2307,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>567628</v>
+        <v>567682</v>
       </c>
       <c r="R18" t="n">
-        <v>6507641</v>
+        <v>6507630</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2355,12 +2337,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2387,60 +2369,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129348519</v>
+        <v>129338383</v>
       </c>
       <c r="B19" t="n">
-        <v>98774</v>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>567686</v>
+        <v>567628</v>
       </c>
       <c r="R19" t="n">
-        <v>6507647</v>
+        <v>6507641</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2478,29 +2448,28 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129338831</v>
+        <v>129346498</v>
       </c>
       <c r="B20" t="n">
-        <v>105840</v>
+        <v>92567</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2508,46 +2477,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221144</v>
+        <v>6031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+          <t>Nedre herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>567680</v>
+        <v>567673</v>
       </c>
       <c r="R20" t="n">
-        <v>6507618</v>
+        <v>6507645</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2574,9 +2534,19 @@
           <t>2025-10-26</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2591,69 +2561,62 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Malin Ringqvist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Malin Ringqvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129348644</v>
+        <v>129273165</v>
       </c>
       <c r="B21" t="n">
-        <v>98774</v>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>567748</v>
+        <v>567782</v>
       </c>
       <c r="R21" t="n">
-        <v>6507663</v>
+        <v>6507769</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2680,12 +2643,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2694,29 +2657,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129339083</v>
+        <v>129271263</v>
       </c>
       <c r="B22" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2743,19 +2705,24 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Nedre herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>567673</v>
+        <v>567692</v>
       </c>
       <c r="R22" t="n">
-        <v>6507645</v>
+        <v>6507635</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2782,12 +2749,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,60 +2769,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Malin Ringqvist</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129340660</v>
+        <v>129271369</v>
       </c>
       <c r="B23" t="n">
-        <v>96263</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>567623</v>
+        <v>567690</v>
       </c>
       <c r="R23" t="n">
-        <v>6507640</v>
+        <v>6507636</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2879,12 +2855,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2911,10 +2887,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129348724</v>
+        <v>129271576</v>
       </c>
       <c r="B24" t="n">
-        <v>98774</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,7 +2917,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2949,22 +2925,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>567722</v>
+        <v>567755</v>
       </c>
       <c r="R24" t="n">
-        <v>6507702</v>
+        <v>6507685</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2988,12 +2961,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-26</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3002,70 +2975,75 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129715546</v>
+        <v>129274008</v>
       </c>
       <c r="B25" t="n">
-        <v>91642</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>567701</v>
+        <v>567685</v>
       </c>
       <c r="R25" t="n">
-        <v>6507721</v>
+        <v>6507629</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3089,12 +3067,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,75 +3081,70 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129715556</v>
+        <v>129339083</v>
       </c>
       <c r="B26" t="n">
-        <v>96262</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>567573</v>
+        <v>567673</v>
       </c>
       <c r="R26" t="n">
-        <v>6507735</v>
+        <v>6507645</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3195,12 +3168,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3209,56 +3182,64 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Malin Ringqvist</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Malin Ringqvist</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129715425</v>
+        <v>129348519</v>
       </c>
       <c r="B27" t="n">
-        <v>92060</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5420</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3266,13 +3247,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>567751</v>
+        <v>567686</v>
       </c>
       <c r="R27" t="n">
-        <v>6507643</v>
+        <v>6507647</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3296,12 +3277,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3317,22 +3298,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129715489</v>
+        <v>129348644</v>
       </c>
       <c r="B28" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3359,10 +3340,14 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
@@ -3372,13 +3357,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>567736</v>
+        <v>567748</v>
       </c>
       <c r="R28" t="n">
-        <v>6507677</v>
+        <v>6507663</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3402,12 +3387,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3423,49 +3408,58 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129715522</v>
+        <v>129348724</v>
       </c>
       <c r="B29" t="n">
-        <v>91649</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3473,13 +3467,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>567730</v>
+        <v>567722</v>
       </c>
       <c r="R29" t="n">
-        <v>6507699</v>
+        <v>6507702</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3503,12 +3497,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3524,22 +3518,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129715500</v>
+        <v>129715241</v>
       </c>
       <c r="B30" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3564,11 +3558,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
@@ -3579,10 +3569,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>567741</v>
+        <v>567688</v>
       </c>
       <c r="R30" t="n">
-        <v>6507694</v>
+        <v>6507631</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3642,41 +3632,38 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129716072</v>
+        <v>129715396</v>
       </c>
       <c r="B31" t="n">
-        <v>92902</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3684,10 +3671,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567681</v>
+        <v>567695</v>
       </c>
       <c r="R31" t="n">
-        <v>6507630</v>
+        <v>6507637</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3747,10 +3734,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129715241</v>
+        <v>129715489</v>
       </c>
       <c r="B32" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3775,7 +3762,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
@@ -3786,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567688</v>
+        <v>567736</v>
       </c>
       <c r="R32" t="n">
-        <v>6507631</v>
+        <v>6507677</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3849,10 +3840,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129715396</v>
+        <v>129715500</v>
       </c>
       <c r="B33" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3877,7 +3868,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
@@ -3888,10 +3883,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567695</v>
+        <v>567741</v>
       </c>
       <c r="R33" t="n">
-        <v>6507637</v>
+        <v>6507694</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3951,51 +3946,57 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129715409</v>
+        <v>129866819</v>
       </c>
       <c r="B34" t="n">
-        <v>91649</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567740</v>
+        <v>567745</v>
       </c>
       <c r="R34" t="n">
-        <v>6507631</v>
+        <v>6507685</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4017,14 +4018,24 @@
           <t>Kvillinge</t>
         </is>
       </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>E-Nor-0875</t>
+        </is>
+      </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Sammanställt av 5 rapporter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4033,29 +4044,32 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson, Emma Nordenberg</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr"/>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129866819</v>
+        <v>129866820</v>
       </c>
       <c r="B35" t="n">
-        <v>98833</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4082,12 +4096,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -4096,13 +4105,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567745</v>
+        <v>567689</v>
       </c>
       <c r="R35" t="n">
-        <v>6507685</v>
+        <v>6507637</v>
       </c>
       <c r="S35" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4126,22 +4135,22 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>E-Nor-0875</t>
+          <t>E-Nor-0874</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Sammanställt av 5 rapporter</t>
+          <t>Sammanställt av 6 rapporter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4161,7 +4170,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Lena Lundin Johansson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
@@ -4172,52 +4181,57 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129866820</v>
+        <v>129338831</v>
       </c>
       <c r="B36" t="n">
-        <v>98920</v>
+        <v>106243</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Nedre Herrgölen, Ög</t>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567689</v>
+        <v>567680</v>
       </c>
       <c r="R36" t="n">
-        <v>6507637</v>
+        <v>6507618</v>
       </c>
       <c r="S36" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4239,24 +4253,14 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>E-Nor-0874</t>
-        </is>
-      </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Sammanställt av 6 rapporter</t>
+          <t>2025-10-26</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4271,19 +4275,307 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lena Lundin Johansson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>103801972</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norrköping, Ög</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>567709</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6507860</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Olle Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Olle Jonsson, Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>129340236</v>
+      </c>
+      <c r="B38" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>567646</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6507635</v>
+      </c>
+      <c r="S38" t="n">
+        <v>15</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>129369141</v>
+      </c>
+      <c r="B39" t="n">
+        <v>93225</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Nedre Herrgölen, Nedre Herrgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>567624</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6507646</v>
+      </c>
+      <c r="S39" t="n">
+        <v>15</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-10-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44688-2025 artfynd.xlsx
+++ b/artfynd/A 44688-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715556</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715546</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273672</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129340660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129716072</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271284</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339186</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129348675</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1578,6 +1623,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273599</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715425</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1776,6 +1831,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271951</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1873,6 +1933,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273994</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715409</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2075,6 +2145,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715522</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271131</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273293</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129274017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129338383</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2570,6 +2665,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129346498</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2672,6 +2772,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129273165</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2778,6 +2883,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271263</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2884,6 +2994,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271369</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2990,6 +3105,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271576</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3096,6 +3216,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129274008</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3197,6 +3322,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129339083</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3307,6 +3437,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129348519</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3417,6 +3552,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129348644</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3527,6 +3667,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129348724</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3629,6 +3774,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715241</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3731,6 +3881,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715396</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3837,6 +3992,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715489</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3943,6 +4103,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129715500</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4063,6 +4228,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866819</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4178,6 +4348,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866820</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4284,6 +4459,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129338831</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4382,6 +4562,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103801972</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4479,6 +4664,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129340236</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4576,8 +4766,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129369141</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>